--- a/data/presentation_schedule.xlsx
+++ b/data/presentation_schedule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,58 @@
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TP012345</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Test Student</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01:00 PM - 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
